--- a/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
+++ b/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbewe\AppData\Local\Classic-Repair-Toolbox\Data\Amstrad CPC 664\MC0005A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbewe\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63ADEBFC-06A7-47D7-B0F6-9E290B889D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67683A1F-D97E-4972-B9D8-4F5DF248DCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="8" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="287">
   <si>
     <t>Name</t>
   </si>
@@ -991,6 +991,12 @@
   </si>
   <si>
     <t>Rabs</t>
+  </si>
+  <si>
+    <t>Schematics</t>
+  </si>
+  <si>
+    <t>https://www.cpcwiki.eu/index.php/Main_Page</t>
   </si>
 </sst>
 </file>
@@ -13552,7 +13558,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCEBA5B-6A50-48EF-B74E-B76FA9984AEF}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.28515625" customWidth="1"/>
@@ -13633,8 +13639,22 @@
         <v>283</v>
       </c>
     </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>285</v>
+      </c>
+      <c r="C11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>286</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D11" r:id="rId1" xr:uid="{9604E299-48FC-4B70-80FB-D23726D038D8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>